--- a/docs/UAT_Testing.xlsx
+++ b/docs/UAT_Testing.xlsx
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -227,6 +227,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3262,8 +3268,8 @@
       <c r="E124" s="7" t="n"/>
       <c r="F124" s="8" t="n"/>
     </row>
-    <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="126" ht="24" customHeight="1">
+      <c r="A126" s="23" t="inlineStr">
         <is>
           <t>Section 5: Security &amp; Input Guardrails</t>
         </is>
@@ -3274,8 +3280,8 @@
       <c r="E126" s="19" t="n"/>
       <c r="F126" s="20" t="n"/>
     </row>
-    <row r="127">
-      <c r="A127" s="6" t="inlineStr">
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="24" t="inlineStr">
         <is>
           <t>5.1 Quote Handling</t>
         </is>
@@ -3286,8 +3292,8 @@
       <c r="E127" s="19" t="n"/>
       <c r="F127" s="20" t="n"/>
     </row>
-    <row r="128">
-      <c r="A128" s="7" t="inlineStr">
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="8" t="inlineStr">
         <is>
           <t>G-01</t>
         </is>
@@ -3310,8 +3316,8 @@
       <c r="E128" s="7" t="n"/>
       <c r="F128" s="8" t="n"/>
     </row>
-    <row r="129">
-      <c r="A129" s="7" t="inlineStr">
+    <row r="129" ht="36" customHeight="1">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>G-02</t>
         </is>
@@ -3334,8 +3340,8 @@
       <c r="E129" s="7" t="n"/>
       <c r="F129" s="8" t="n"/>
     </row>
-    <row r="130">
-      <c r="A130" s="7" t="inlineStr">
+    <row r="130" ht="36" customHeight="1">
+      <c r="A130" s="8" t="inlineStr">
         <is>
           <t>G-03</t>
         </is>
@@ -3358,8 +3364,8 @@
       <c r="E130" s="7" t="n"/>
       <c r="F130" s="8" t="n"/>
     </row>
-    <row r="131">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="8" t="inlineStr">
         <is>
           <t>G-04</t>
         </is>
@@ -3382,8 +3388,8 @@
       <c r="E131" s="7" t="n"/>
       <c r="F131" s="8" t="n"/>
     </row>
-    <row r="132">
-      <c r="A132" s="7" t="inlineStr">
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t>G-05</t>
         </is>
@@ -3406,8 +3412,8 @@
       <c r="E132" s="7" t="n"/>
       <c r="F132" s="8" t="n"/>
     </row>
-    <row r="133">
-      <c r="A133" s="6" t="inlineStr">
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="24" t="inlineStr">
         <is>
           <t>5.2 Prompt Injection Detection</t>
         </is>
@@ -3418,8 +3424,8 @@
       <c r="E133" s="19" t="n"/>
       <c r="F133" s="20" t="n"/>
     </row>
-    <row r="134">
-      <c r="A134" s="7" t="inlineStr">
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t>G-06</t>
         </is>
@@ -3442,8 +3448,8 @@
       <c r="E134" s="7" t="n"/>
       <c r="F134" s="8" t="n"/>
     </row>
-    <row r="135">
-      <c r="A135" s="7" t="inlineStr">
+    <row r="135" ht="36" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>G-07</t>
         </is>
@@ -3466,8 +3472,8 @@
       <c r="E135" s="7" t="n"/>
       <c r="F135" s="8" t="n"/>
     </row>
-    <row r="136">
-      <c r="A136" s="7" t="inlineStr">
+    <row r="136" ht="36" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>G-08</t>
         </is>
@@ -3490,8 +3496,8 @@
       <c r="E136" s="7" t="n"/>
       <c r="F136" s="8" t="n"/>
     </row>
-    <row r="137">
-      <c r="A137" s="7" t="inlineStr">
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>G-09</t>
         </is>
@@ -3514,8 +3520,8 @@
       <c r="E137" s="7" t="n"/>
       <c r="F137" s="8" t="n"/>
     </row>
-    <row r="138">
-      <c r="A138" s="7" t="inlineStr">
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>G-10</t>
         </is>
@@ -3538,8 +3544,8 @@
       <c r="E138" s="7" t="n"/>
       <c r="F138" s="8" t="n"/>
     </row>
-    <row r="139">
-      <c r="A139" s="6" t="inlineStr">
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="24" t="inlineStr">
         <is>
           <t>5.3 Input Sanitization</t>
         </is>
@@ -3550,8 +3556,8 @@
       <c r="E139" s="19" t="n"/>
       <c r="F139" s="20" t="n"/>
     </row>
-    <row r="140">
-      <c r="A140" s="7" t="inlineStr">
+    <row r="140" ht="36" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>G-11</t>
         </is>
@@ -3574,8 +3580,8 @@
       <c r="E140" s="7" t="n"/>
       <c r="F140" s="8" t="n"/>
     </row>
-    <row r="141">
-      <c r="A141" s="7" t="inlineStr">
+    <row r="141" ht="36" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>G-12</t>
         </is>
@@ -3598,8 +3604,8 @@
       <c r="E141" s="7" t="n"/>
       <c r="F141" s="8" t="n"/>
     </row>
-    <row r="142">
-      <c r="A142" s="7" t="inlineStr">
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>G-13</t>
         </is>
@@ -3622,8 +3628,8 @@
       <c r="E142" s="7" t="n"/>
       <c r="F142" s="8" t="n"/>
     </row>
-    <row r="143">
-      <c r="A143" s="6" t="inlineStr">
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="24" t="inlineStr">
         <is>
           <t>5.4 Output Leakage Prevention</t>
         </is>
@@ -3634,8 +3640,8 @@
       <c r="E143" s="19" t="n"/>
       <c r="F143" s="20" t="n"/>
     </row>
-    <row r="144">
-      <c r="A144" s="7" t="inlineStr">
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>G-14</t>
         </is>
@@ -3658,8 +3664,8 @@
       <c r="E144" s="7" t="n"/>
       <c r="F144" s="8" t="n"/>
     </row>
-    <row r="145">
-      <c r="A145" s="7" t="inlineStr">
+    <row r="145" ht="36" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>G-15</t>
         </is>
@@ -3682,9 +3688,9 @@
       <c r="E145" s="7" t="n"/>
       <c r="F145" s="8" t="n"/>
     </row>
-    <row r="146"/>
-    <row r="147">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="146" ht="15" customHeight="1"/>
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="23" t="inlineStr">
         <is>
           <t>Section 6: Author Display &amp; Data Formatting</t>
         </is>
@@ -3695,8 +3701,8 @@
       <c r="E147" s="19" t="n"/>
       <c r="F147" s="20" t="n"/>
     </row>
-    <row r="148">
-      <c r="A148" s="6" t="inlineStr">
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="24" t="inlineStr">
         <is>
           <t>6.1 Author Display in CSV Query Responses</t>
         </is>
@@ -3707,8 +3713,8 @@
       <c r="E148" s="19" t="n"/>
       <c r="F148" s="20" t="n"/>
     </row>
-    <row r="149">
-      <c r="A149" s="7" t="inlineStr">
+    <row r="149" ht="36" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>D-01</t>
         </is>
@@ -3731,8 +3737,8 @@
       <c r="E149" s="7" t="n"/>
       <c r="F149" s="8" t="n"/>
     </row>
-    <row r="150">
-      <c r="A150" s="7" t="inlineStr">
+    <row r="150" ht="36" customHeight="1">
+      <c r="A150" s="8" t="inlineStr">
         <is>
           <t>D-02</t>
         </is>
@@ -3755,8 +3761,8 @@
       <c r="E150" s="7" t="n"/>
       <c r="F150" s="8" t="n"/>
     </row>
-    <row r="151">
-      <c r="A151" s="7" t="inlineStr">
+    <row r="151" ht="36" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t>D-03</t>
         </is>
@@ -3779,8 +3785,8 @@
       <c r="E151" s="7" t="n"/>
       <c r="F151" s="8" t="n"/>
     </row>
-    <row r="152">
-      <c r="A152" s="7" t="inlineStr">
+    <row r="152" ht="36" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>D-04</t>
         </is>
@@ -3803,8 +3809,8 @@
       <c r="E152" s="7" t="n"/>
       <c r="F152" s="8" t="n"/>
     </row>
-    <row r="153">
-      <c r="A153" s="7" t="inlineStr">
+    <row r="153" ht="36" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>D-05</t>
         </is>
@@ -3827,8 +3833,8 @@
       <c r="E153" s="7" t="n"/>
       <c r="F153" s="8" t="n"/>
     </row>
-    <row r="154">
-      <c r="A154" s="6" t="inlineStr">
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="24" t="inlineStr">
         <is>
           <t>6.2 Topic Query Author Display</t>
         </is>
@@ -3839,8 +3845,8 @@
       <c r="E154" s="19" t="n"/>
       <c r="F154" s="20" t="n"/>
     </row>
-    <row r="155">
-      <c r="A155" s="7" t="inlineStr">
+    <row r="155" ht="36" customHeight="1">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t>D-06</t>
         </is>
@@ -3863,8 +3869,8 @@
       <c r="E155" s="7" t="n"/>
       <c r="F155" s="8" t="n"/>
     </row>
-    <row r="156">
-      <c r="A156" s="7" t="inlineStr">
+    <row r="156" ht="36" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>D-07</t>
         </is>
@@ -3887,8 +3893,8 @@
       <c r="E156" s="7" t="n"/>
       <c r="F156" s="8" t="n"/>
     </row>
-    <row r="157">
-      <c r="A157" s="7" t="inlineStr">
+    <row r="157" ht="36" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>D-08</t>
         </is>
@@ -3911,9 +3917,9 @@
       <c r="E157" s="7" t="n"/>
       <c r="F157" s="8" t="n"/>
     </row>
-    <row r="158"/>
-    <row r="159">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="158" ht="15" customHeight="1"/>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="23" t="inlineStr">
         <is>
           <t>Section 7: UI Display Fixes</t>
         </is>
@@ -3924,8 +3930,8 @@
       <c r="E159" s="19" t="n"/>
       <c r="F159" s="20" t="n"/>
     </row>
-    <row r="160">
-      <c r="A160" s="6" t="inlineStr">
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="24" t="inlineStr">
         <is>
           <t>7.1 Hero Title Tamil Rendering</t>
         </is>
@@ -3936,8 +3942,8 @@
       <c r="E160" s="19" t="n"/>
       <c r="F160" s="20" t="n"/>
     </row>
-    <row r="161">
-      <c r="A161" s="7" t="inlineStr">
+    <row r="161" ht="36" customHeight="1">
+      <c r="A161" s="8" t="inlineStr">
         <is>
           <t>U-01</t>
         </is>
@@ -3960,8 +3966,8 @@
       <c r="E161" s="7" t="n"/>
       <c r="F161" s="8" t="n"/>
     </row>
-    <row r="162">
-      <c r="A162" s="7" t="inlineStr">
+    <row r="162" ht="36" customHeight="1">
+      <c r="A162" s="8" t="inlineStr">
         <is>
           <t>U-02</t>
         </is>
@@ -3984,8 +3990,8 @@
       <c r="E162" s="7" t="n"/>
       <c r="F162" s="8" t="n"/>
     </row>
-    <row r="163">
-      <c r="A163" s="7" t="inlineStr">
+    <row r="163" ht="36" customHeight="1">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>U-03</t>
         </is>
@@ -4008,8 +4014,8 @@
       <c r="E163" s="7" t="n"/>
       <c r="F163" s="8" t="n"/>
     </row>
-    <row r="164">
-      <c r="A164" s="6" t="inlineStr">
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="24" t="inlineStr">
         <is>
           <t>7.2 Conversation History</t>
         </is>
@@ -4020,8 +4026,8 @@
       <c r="E164" s="19" t="n"/>
       <c r="F164" s="20" t="n"/>
     </row>
-    <row r="165">
-      <c r="A165" s="7" t="inlineStr">
+    <row r="165" ht="36" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
         <is>
           <t>U-04</t>
         </is>
@@ -4044,8 +4050,8 @@
       <c r="E165" s="7" t="n"/>
       <c r="F165" s="8" t="n"/>
     </row>
-    <row r="166">
-      <c r="A166" s="7" t="inlineStr">
+    <row r="166" ht="36" customHeight="1">
+      <c r="A166" s="8" t="inlineStr">
         <is>
           <t>U-05</t>
         </is>
@@ -4068,8 +4074,8 @@
       <c r="E166" s="7" t="n"/>
       <c r="F166" s="8" t="n"/>
     </row>
-    <row r="167">
-      <c r="A167" s="7" t="inlineStr">
+    <row r="167" ht="36" customHeight="1">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t>U-06</t>
         </is>
@@ -4092,8 +4098,8 @@
       <c r="E167" s="7" t="n"/>
       <c r="F167" s="8" t="n"/>
     </row>
-    <row r="168">
-      <c r="A168" s="6" t="inlineStr">
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="24" t="inlineStr">
         <is>
           <t>7.3 Image Proxy</t>
         </is>
@@ -4104,8 +4110,8 @@
       <c r="E168" s="19" t="n"/>
       <c r="F168" s="20" t="n"/>
     </row>
-    <row r="169">
-      <c r="A169" s="7" t="inlineStr">
+    <row r="169" ht="36" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t>U-07</t>
         </is>
@@ -4128,8 +4134,8 @@
       <c r="E169" s="7" t="n"/>
       <c r="F169" s="8" t="n"/>
     </row>
-    <row r="170">
-      <c r="A170" s="7" t="inlineStr">
+    <row r="170" ht="36" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
         <is>
           <t>U-08</t>
         </is>
@@ -4152,8 +4158,8 @@
       <c r="E170" s="7" t="n"/>
       <c r="F170" s="8" t="n"/>
     </row>
-    <row r="171">
-      <c r="A171" s="7" t="inlineStr">
+    <row r="171" ht="36" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
         <is>
           <t>U-09</t>
         </is>
@@ -4176,8 +4182,8 @@
       <c r="E171" s="7" t="n"/>
       <c r="F171" s="8" t="n"/>
     </row>
-    <row r="172">
-      <c r="A172" s="7" t="inlineStr">
+    <row r="172" ht="36" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
         <is>
           <t>U-10</t>
         </is>
@@ -4200,9 +4206,9 @@
       <c r="E172" s="7" t="n"/>
       <c r="F172" s="8" t="n"/>
     </row>
-    <row r="173"/>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr">
+    <row r="173" ht="15" customHeight="1"/>
+    <row r="174" ht="24" customHeight="1">
+      <c r="A174" s="23" t="inlineStr">
         <is>
           <t>Section 8: Categories — Taxonomy &amp; Tag System</t>
         </is>
@@ -4213,8 +4219,8 @@
       <c r="E174" s="19" t="n"/>
       <c r="F174" s="20" t="n"/>
     </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="24" t="inlineStr">
         <is>
           <t>8.1 Tag Taxonomy Completeness</t>
         </is>
@@ -4225,8 +4231,8 @@
       <c r="E175" s="19" t="n"/>
       <c r="F175" s="20" t="n"/>
     </row>
-    <row r="176">
-      <c r="A176" s="7" t="inlineStr">
+    <row r="176" ht="36" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>CT-01</t>
         </is>
@@ -4249,8 +4255,8 @@
       <c r="E176" s="7" t="n"/>
       <c r="F176" s="8" t="n"/>
     </row>
-    <row r="177">
-      <c r="A177" s="7" t="inlineStr">
+    <row r="177" ht="36" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
         <is>
           <t>CT-02</t>
         </is>
@@ -4273,8 +4279,8 @@
       <c r="E177" s="7" t="n"/>
       <c r="F177" s="8" t="n"/>
     </row>
-    <row r="178">
-      <c r="A178" s="7" t="inlineStr">
+    <row r="178" ht="36" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>CT-03</t>
         </is>
@@ -4297,8 +4303,8 @@
       <c r="E178" s="7" t="n"/>
       <c r="F178" s="8" t="n"/>
     </row>
-    <row r="179">
-      <c r="A179" s="7" t="inlineStr">
+    <row r="179" ht="36" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t>CT-04</t>
         </is>
@@ -4321,8 +4327,8 @@
       <c r="E179" s="7" t="n"/>
       <c r="F179" s="8" t="n"/>
     </row>
-    <row r="180">
-      <c r="A180" s="7" t="inlineStr">
+    <row r="180" ht="36" customHeight="1">
+      <c r="A180" s="8" t="inlineStr">
         <is>
           <t>CT-05</t>
         </is>
@@ -4345,8 +4351,8 @@
       <c r="E180" s="7" t="n"/>
       <c r="F180" s="8" t="n"/>
     </row>
-    <row r="181">
-      <c r="A181" s="7" t="inlineStr">
+    <row r="181" ht="36" customHeight="1">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t>CT-06</t>
         </is>
@@ -4369,8 +4375,8 @@
       <c r="E181" s="7" t="n"/>
       <c r="F181" s="8" t="n"/>
     </row>
-    <row r="182">
-      <c r="A182" s="7" t="inlineStr">
+    <row r="182" ht="36" customHeight="1">
+      <c r="A182" s="8" t="inlineStr">
         <is>
           <t>CT-07</t>
         </is>
@@ -4393,8 +4399,8 @@
       <c r="E182" s="7" t="n"/>
       <c r="F182" s="8" t="n"/>
     </row>
-    <row r="183">
-      <c r="A183" s="7" t="inlineStr">
+    <row r="183" ht="36" customHeight="1">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>CT-08</t>
         </is>
@@ -4417,8 +4423,8 @@
       <c r="E183" s="7" t="n"/>
       <c r="F183" s="8" t="n"/>
     </row>
-    <row r="184">
-      <c r="A184" s="7" t="inlineStr">
+    <row r="184" ht="36" customHeight="1">
+      <c r="A184" s="8" t="inlineStr">
         <is>
           <t>CT-09</t>
         </is>
@@ -4441,8 +4447,8 @@
       <c r="E184" s="7" t="n"/>
       <c r="F184" s="8" t="n"/>
     </row>
-    <row r="185">
-      <c r="A185" s="6" t="inlineStr">
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="24" t="inlineStr">
         <is>
           <t>8.2 Tag Assignment Quality</t>
         </is>
@@ -4453,8 +4459,8 @@
       <c r="E185" s="19" t="n"/>
       <c r="F185" s="20" t="n"/>
     </row>
-    <row r="186">
-      <c r="A186" s="7" t="inlineStr">
+    <row r="186" ht="36" customHeight="1">
+      <c r="A186" s="8" t="inlineStr">
         <is>
           <t>CT-10</t>
         </is>
@@ -4477,8 +4483,8 @@
       <c r="E186" s="7" t="n"/>
       <c r="F186" s="8" t="n"/>
     </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr">
+    <row r="187" ht="36" customHeight="1">
+      <c r="A187" s="8" t="inlineStr">
         <is>
           <t>CT-11</t>
         </is>
@@ -4501,8 +4507,8 @@
       <c r="E187" s="7" t="n"/>
       <c r="F187" s="8" t="n"/>
     </row>
-    <row r="188">
-      <c r="A188" s="7" t="inlineStr">
+    <row r="188" ht="36" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
         <is>
           <t>CT-12</t>
         </is>
@@ -4525,8 +4531,8 @@
       <c r="E188" s="7" t="n"/>
       <c r="F188" s="8" t="n"/>
     </row>
-    <row r="189">
-      <c r="A189" s="7" t="inlineStr">
+    <row r="189" ht="36" customHeight="1">
+      <c r="A189" s="8" t="inlineStr">
         <is>
           <t>CT-13</t>
         </is>
@@ -4549,8 +4555,8 @@
       <c r="E189" s="7" t="n"/>
       <c r="F189" s="8" t="n"/>
     </row>
-    <row r="190">
-      <c r="A190" s="7" t="inlineStr">
+    <row r="190" ht="36" customHeight="1">
+      <c r="A190" s="8" t="inlineStr">
         <is>
           <t>CT-14</t>
         </is>
@@ -4573,8 +4579,8 @@
       <c r="E190" s="7" t="n"/>
       <c r="F190" s="8" t="n"/>
     </row>
-    <row r="191">
-      <c r="A191" s="7" t="inlineStr">
+    <row r="191" ht="36" customHeight="1">
+      <c r="A191" s="8" t="inlineStr">
         <is>
           <t>CT-15</t>
         </is>
@@ -4597,8 +4603,8 @@
       <c r="E191" s="7" t="n"/>
       <c r="F191" s="8" t="n"/>
     </row>
-    <row r="192">
-      <c r="A192" s="7" t="inlineStr">
+    <row r="192" ht="36" customHeight="1">
+      <c r="A192" s="8" t="inlineStr">
         <is>
           <t>CT-16</t>
         </is>
@@ -4621,8 +4627,8 @@
       <c r="E192" s="7" t="n"/>
       <c r="F192" s="8" t="n"/>
     </row>
-    <row r="193">
-      <c r="A193" s="6" t="inlineStr">
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="24" t="inlineStr">
         <is>
           <t>8.3 Tag API Responses</t>
         </is>
@@ -4633,8 +4639,8 @@
       <c r="E193" s="19" t="n"/>
       <c r="F193" s="20" t="n"/>
     </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
+    <row r="194" ht="36" customHeight="1">
+      <c r="A194" s="8" t="inlineStr">
         <is>
           <t>CT-17</t>
         </is>
@@ -4657,8 +4663,8 @@
       <c r="E194" s="7" t="n"/>
       <c r="F194" s="8" t="n"/>
     </row>
-    <row r="195">
-      <c r="A195" s="7" t="inlineStr">
+    <row r="195" ht="36" customHeight="1">
+      <c r="A195" s="8" t="inlineStr">
         <is>
           <t>CT-18</t>
         </is>
@@ -4681,8 +4687,8 @@
       <c r="E195" s="7" t="n"/>
       <c r="F195" s="8" t="n"/>
     </row>
-    <row r="196">
-      <c r="A196" s="7" t="inlineStr">
+    <row r="196" ht="36" customHeight="1">
+      <c r="A196" s="8" t="inlineStr">
         <is>
           <t>CT-19</t>
         </is>
@@ -4705,8 +4711,8 @@
       <c r="E196" s="7" t="n"/>
       <c r="F196" s="8" t="n"/>
     </row>
-    <row r="197">
-      <c r="A197" s="7" t="inlineStr">
+    <row r="197" ht="36" customHeight="1">
+      <c r="A197" s="8" t="inlineStr">
         <is>
           <t>CT-20</t>
         </is>
@@ -4729,8 +4735,8 @@
       <c r="E197" s="7" t="n"/>
       <c r="F197" s="8" t="n"/>
     </row>
-    <row r="198">
-      <c r="A198" s="7" t="inlineStr">
+    <row r="198" ht="36" customHeight="1">
+      <c r="A198" s="8" t="inlineStr">
         <is>
           <t>CT-21</t>
         </is>
@@ -4753,8 +4759,8 @@
       <c r="E198" s="7" t="n"/>
       <c r="F198" s="8" t="n"/>
     </row>
-    <row r="199">
-      <c r="A199" s="6" t="inlineStr">
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="24" t="inlineStr">
         <is>
           <t>8.4 Tags in AI Chat Sources</t>
         </is>
@@ -4765,8 +4771,8 @@
       <c r="E199" s="19" t="n"/>
       <c r="F199" s="20" t="n"/>
     </row>
-    <row r="200">
-      <c r="A200" s="7" t="inlineStr">
+    <row r="200" ht="36" customHeight="1">
+      <c r="A200" s="8" t="inlineStr">
         <is>
           <t>CT-22</t>
         </is>
@@ -4789,8 +4795,8 @@
       <c r="E200" s="7" t="n"/>
       <c r="F200" s="8" t="n"/>
     </row>
-    <row r="201">
-      <c r="A201" s="7" t="inlineStr">
+    <row r="201" ht="36" customHeight="1">
+      <c r="A201" s="8" t="inlineStr">
         <is>
           <t>CT-23</t>
         </is>
@@ -4813,8 +4819,8 @@
       <c r="E201" s="7" t="n"/>
       <c r="F201" s="8" t="n"/>
     </row>
-    <row r="202">
-      <c r="A202" s="7" t="inlineStr">
+    <row r="202" ht="36" customHeight="1">
+      <c r="A202" s="8" t="inlineStr">
         <is>
           <t>CT-24</t>
         </is>
@@ -4837,8 +4843,8 @@
       <c r="E202" s="7" t="n"/>
       <c r="F202" s="8" t="n"/>
     </row>
-    <row r="203">
-      <c r="A203" s="6" t="inlineStr">
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="24" t="inlineStr">
         <is>
           <t>8.5 Tag Consistency</t>
         </is>
@@ -4849,8 +4855,8 @@
       <c r="E203" s="19" t="n"/>
       <c r="F203" s="20" t="n"/>
     </row>
-    <row r="204">
-      <c r="A204" s="7" t="inlineStr">
+    <row r="204" ht="36" customHeight="1">
+      <c r="A204" s="8" t="inlineStr">
         <is>
           <t>CT-25</t>
         </is>
@@ -4873,8 +4879,8 @@
       <c r="E204" s="7" t="n"/>
       <c r="F204" s="8" t="n"/>
     </row>
-    <row r="205">
-      <c r="A205" s="7" t="inlineStr">
+    <row r="205" ht="36" customHeight="1">
+      <c r="A205" s="8" t="inlineStr">
         <is>
           <t>CT-26</t>
         </is>
